--- a/Scenario Files/ShowerScenarios.xlsx
+++ b/Scenario Files/ShowerScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3866,6 +3866,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>With a high-flow showerhead and small tank on a cold morning, how long should I shower?</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Altoona, PA</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" t="n">
+        <v>40</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>240</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>18</v>
+      </c>
+      <c r="I79" t="n">
+        <v>120</v>
+      </c>
+      <c r="J79" t="n">
+        <v>4</v>
+      </c>
+      <c r="K79" t="n">
+        <v>6</v>
+      </c>
+      <c r="L79" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>On a hot day with a low-flow showerhead, what shower duration makes sense?</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Chester, PA</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>30</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F80" t="n">
+        <v>150</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Condo</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>90</v>
+      </c>
+      <c r="I80" t="n">
+        <v>115</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>7</v>
+      </c>
+      <c r="L80" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>With six people sharing a tank tonight, how long should showers be?</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Johnstown, PA</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" t="n">
+        <v>50</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F81" t="n">
+        <v>340</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>40</v>
+      </c>
+      <c r="I81" t="n">
+        <v>120</v>
+      </c>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Scenario Files/ShowerScenarios.xlsx
+++ b/Scenario Files/ShowerScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,62 +419,62 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>question</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Occupants</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Tank Size</t>
+          <t>tank_size</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>GPM</t>
+          <t>gpm</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Utility Budget</t>
+          <t>utility_budget</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Housing Type</t>
+          <t>housing_type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Outdoor Temp</t>
+          <t>outdoor_temp</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Water Heater Temp</t>
+          <t>water_heater_temp</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Alternative 1</t>
+          <t>alternative_1</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Alternative 2</t>
+          <t>alternative_2</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Alternative 3</t>
+          <t>alternative_3</t>
         </is>
       </c>
     </row>
